--- a/Data/dictionnaires.xlsx
+++ b/Data/dictionnaires.xlsx
@@ -227,6 +227,15 @@
   </x:si>
   <x:si>
     <x:t>Basketball</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TitreStaff</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Soignant</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Entraineur</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1470,6 +1479,70 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H29" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="0">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H30" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
